--- a/example/formUploadBerhasil/formCabangPusatBedaEntitas.xlsx
+++ b/example/formUploadBerhasil/formCabangPusatBedaEntitas.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Project 2025\dashmad\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Project 2025\dashmad\example\formUploadBerhasil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8330704B-4D69-4DE7-B7DD-0BD57619921B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A5BB3D-B5E3-48CD-AE8B-B9A0D007D829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
     <t>npwpCabang</t>
   </si>
@@ -173,6 +172,12 @@
   </si>
   <si>
     <t>3578084411350000</t>
+  </si>
+  <si>
+    <t>066538869607000</t>
+  </si>
+  <si>
+    <t>060565298606000</t>
   </si>
 </sst>
 </file>
@@ -506,7 +511,7 @@
     <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
@@ -625,8 +630,8 @@
       <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="M2">
-        <v>66538869607000</v>
+      <c r="M2" t="s">
+        <v>49</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -700,8 +705,8 @@
       <c r="L3" t="s">
         <v>34</v>
       </c>
-      <c r="M3">
-        <v>60565298606000</v>
+      <c r="M3" t="s">
+        <v>50</v>
       </c>
       <c r="N3" t="s">
         <v>37</v>
@@ -742,55 +747,6 @@
       </c>
       <c r="Z3">
         <v>45385</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CD962B-1CEF-4CC5-BD81-DF6AE18D0932}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
